--- a/astro-site/public/dl/guia-pasteleria-obrador/plan-financiero-3-anos-pasteleria.xlsx
+++ b/astro-site/public/dl/guia-pasteleria-obrador/plan-financiero-3-anos-pasteleria.xlsx
@@ -2378,7 +2378,7 @@
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>Cuánto puedes caer sobre lo previsto antes de entrar en pérdidas.</t>
+          <t>Cuánto deben superar las ventas previstas a las del punto de equilibrio. La caída que aguantas antes de entrar en pérdidas es algo menor: con un 15 % de holgura, un 13 % de lo previsto.</t>
         </is>
       </c>
     </row>
@@ -4839,7 +4839,7 @@
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>Cuánto puedes caer sobre lo previsto antes de no poder pagar los fijos y la cuota. El mínimo exigible está en «0. Supuestos».</t>
+          <t>Cuánto superan tus ventas previstas a las del equilibrio de caja. La caída que aguantas antes de no poder pagar los fijos y la cuota es algo menor: con un 25 % de holgura, un 20 %. El mínimo exigible está en «0. Supuestos».</t>
         </is>
       </c>
     </row>

--- a/astro-site/public/dl/guia-pasteleria-obrador/plan-financiero-3-anos-pasteleria.xlsx
+++ b/astro-site/public/dl/guia-pasteleria-obrador/plan-financiero-3-anos-pasteleria.xlsx
@@ -2378,7 +2378,7 @@
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>Cuánto deben superar las ventas previstas a las del punto de equilibrio. La caída que aguantas antes de entrar en pérdidas es algo menor: con un 15 % de holgura, un 13 % de lo previsto.</t>
+          <t>Cuánto deben superar las ventas previstas a las del equilibrio de caja (costes fijos y cuota del préstamo). La caída que aguantas es algo menor: con un 15 % de holgura, un 13 % de lo previsto.</t>
         </is>
       </c>
     </row>

--- a/astro-site/public/dl/guia-pasteleria-obrador/plan-financiero-3-anos-pasteleria.xlsx
+++ b/astro-site/public/dl/guia-pasteleria-obrador/plan-financiero-3-anos-pasteleria.xlsx
@@ -2378,7 +2378,7 @@
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>Cuánto puedes caer sobre lo previsto antes de entrar en pérdidas.</t>
+          <t>Cuánto deben superar las ventas previstas a las del equilibrio de caja (costes fijos y cuota del préstamo). La caída que aguantas es algo menor: con un 15 % de holgura, un 13 % de lo previsto.</t>
         </is>
       </c>
     </row>
@@ -4839,7 +4839,7 @@
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>Cuánto puedes caer sobre lo previsto antes de no poder pagar los fijos y la cuota. El mínimo exigible está en «0. Supuestos».</t>
+          <t>Cuánto superan tus ventas previstas a las del equilibrio de caja. La caída que aguantas antes de no poder pagar los fijos y la cuota es algo menor: con un 25 % de holgura, un 20 %. El mínimo exigible está en «0. Supuestos».</t>
         </is>
       </c>
     </row>
